--- a/fixtures/sanitized/m5/full-import-invalid.xlsx
+++ b/fixtures/sanitized/m5/full-import-invalid.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="128">
   <si>
     <t>template_version</t>
   </si>
@@ -39,7 +39,7 @@
     <t>ui_locale</t>
   </si>
   <si>
-    <t>ledgerkit-workbook-v1.3</t>
+    <t>ledgerkit-workbook-v1.4</t>
   </si>
   <si>
     <t>CNY</t>
@@ -216,6 +216,24 @@
     <t>display_label</t>
   </si>
   <si>
+    <t>fx_override_currency</t>
+  </si>
+  <si>
+    <t>fx_override_value</t>
+  </si>
+  <si>
+    <t>fx_override_reason</t>
+  </si>
+  <si>
+    <t>fee_fx_override_currency</t>
+  </si>
+  <si>
+    <t>fee_fx_override_value</t>
+  </si>
+  <si>
+    <t>fee_fx_override_reason</t>
+  </si>
+  <si>
     <t>2026-02-01</t>
   </si>
   <si>
@@ -244,6 +262,24 @@
   </si>
   <si>
     <t>to_amount</t>
+  </si>
+  <si>
+    <t>from_fx_override_currency</t>
+  </si>
+  <si>
+    <t>from_fx_override_value</t>
+  </si>
+  <si>
+    <t>from_fx_override_reason</t>
+  </si>
+  <si>
+    <t>to_fx_override_currency</t>
+  </si>
+  <si>
+    <t>to_fx_override_value</t>
+  </si>
+  <si>
+    <t>to_fx_override_reason</t>
   </si>
   <si>
     <t>settlement_account_legacy_id</t>
@@ -747,13 +783,13 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C1" t="s">
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E1" t="s">
         <v>10</v>
@@ -761,13 +797,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
         <v>26</v>
@@ -788,16 +824,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E1" t="s">
         <v>45</v>
@@ -808,13 +844,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
         <v>26</v>
@@ -833,10 +869,10 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>49</v>
       </c>
@@ -847,28 +883,28 @@
         <v>51</v>
       </c>
       <c r="D1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="G1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I1" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="J1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="K1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="L1" t="s">
         <v>58</v>
@@ -877,27 +913,36 @@
         <v>54</v>
       </c>
       <c r="N1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="O1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+        <v>107</v>
+      </c>
+      <c r="P1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F2" t="s">
         <v>23</v>
@@ -906,7 +951,7 @@
         <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="I2" t="s">
         <v>28</v>
@@ -924,31 +969,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D1" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="E1" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F1" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="G1" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="H1" t="s">
         <v>18</v>
       </c>
       <c r="I1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -963,30 +1008,30 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D1" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
         <v>42</v>
@@ -1004,22 +1049,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D1" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F1" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1258,10 +1303,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>49</v>
       </c>
@@ -1304,16 +1349,34 @@
       <c r="N1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -1325,19 +1388,19 @@
         <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
         <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1346,36 +1409,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1388,16 +1421,55 @@
         <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="F1" t="s">
-        <v>71</v>
+        <v>56</v>
+      </c>
+      <c r="G1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:18">
+      <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" t="s">
+        <v>77</v>
       </c>
       <c r="G1" t="s">
         <v>57</v>
@@ -1407,6 +1479,33 @@
       </c>
       <c r="I1" t="s">
         <v>56</v>
+      </c>
+      <c r="J1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M1" t="s">
+        <v>81</v>
+      </c>
+      <c r="N1" t="s">
+        <v>82</v>
+      </c>
+      <c r="O1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>66</v>
+      </c>
+      <c r="R1" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1427,13 +1526,13 @@
         <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F1" t="s">
         <v>10</v>
@@ -1447,7 +1546,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -1456,10 +1555,10 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
